--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(RSI&KDJ)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(RSI&KDJ)cn.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="34">
   <si>
     <t>in practice</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -182,6 +182,10 @@
   </si>
   <si>
     <t>成交均量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>总资产</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -663,7 +667,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -843,6 +847,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -852,7 +859,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1031,6 +1038,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -1074,7 +1084,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1254,6 +1264,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1263,7 +1276,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1443,6 +1456,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>16470742.053078819</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>16842108.331714839</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1485,7 +1501,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1665,6 +1681,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1674,7 +1693,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1854,6 +1873,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>7109407.2353513949</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>7480773.5139874145</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1875,11 +1897,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="440983936"/>
-        <c:axId val="440985472"/>
+        <c:axId val="459322880"/>
+        <c:axId val="459324416"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="440983936"/>
+        <c:axId val="459322880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1922,14 +1944,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="440985472"/>
+        <c:crossAx val="459324416"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="440985472"/>
+        <c:axId val="459324416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1980,7 +2002,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="440983936"/>
+        <c:crossAx val="459322880"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2171,7 +2193,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2351,6 +2373,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-329147.77001413936</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-915628.10722505616</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2370,8 +2395,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="495759744"/>
-        <c:axId val="495757952"/>
+        <c:axId val="537606016"/>
+        <c:axId val="537604480"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2396,7 +2421,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2576,6 +2601,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2585,7 +2613,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2765,6 +2793,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2786,11 +2817,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="495750528"/>
-        <c:axId val="495756416"/>
+        <c:axId val="526898304"/>
+        <c:axId val="526899840"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="495750528"/>
+        <c:axId val="526898304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2833,14 +2864,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="495756416"/>
+        <c:crossAx val="526899840"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="495756416"/>
+        <c:axId val="526899840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2891,12 +2922,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="495750528"/>
+        <c:crossAx val="526898304"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="495757952"/>
+        <c:axId val="537604480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2933,12 +2964,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="495759744"/>
+        <c:crossAx val="537606016"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="495759744"/>
+        <c:axId val="537606016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2947,7 +2978,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="495757952"/>
+        <c:crossAx val="537604480"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3126,7 +3157,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3306,6 +3337,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3315,7 +3349,7 @@
               <c:f>'模型四 (3)PE副本成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3494,6 +3528,9 @@
                   <c:v>77414706.150887698</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>77414706.150887698</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>77414706.150887698</c:v>
                 </c:pt>
               </c:numCache>
@@ -3537,7 +3574,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3717,6 +3754,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3726,7 +3766,7 @@
               <c:f>'模型四 (3)PE副本成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3906,6 +3946,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>150048200.74916655</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>153627041.337863</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3948,7 +3991,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4128,6 +4171,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4137,7 +4183,7 @@
               <c:f>'模型四 (3)PE副本成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4317,6 +4363,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>72633494.59827885</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>76212335.1869753</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4338,11 +4387,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="497626496"/>
-        <c:axId val="497628288"/>
+        <c:axId val="539284608"/>
+        <c:axId val="539286144"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="497626496"/>
+        <c:axId val="539284608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4385,14 +4434,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="497628288"/>
+        <c:crossAx val="539286144"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="497628288"/>
+        <c:axId val="539286144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4443,7 +4492,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="497626496"/>
+        <c:crossAx val="539284608"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4634,7 +4683,7 @@
               <c:f>'模型四 (3)PE副本成交量'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4814,6 +4863,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-2083411.4657620986</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-10715332.987082755</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4833,8 +4885,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="498574080"/>
-        <c:axId val="498564096"/>
+        <c:axId val="539355392"/>
+        <c:axId val="539353856"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4859,7 +4911,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5039,6 +5091,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5048,7 +5103,7 @@
               <c:f>'模型四 (3)PE副本成交量'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5228,6 +5283,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5249,11 +5307,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="498561024"/>
-        <c:axId val="498562560"/>
+        <c:axId val="539330048"/>
+        <c:axId val="539331584"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="498561024"/>
+        <c:axId val="539330048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5296,14 +5354,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="498562560"/>
+        <c:crossAx val="539331584"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="498562560"/>
+        <c:axId val="539331584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5354,12 +5412,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="498561024"/>
+        <c:crossAx val="539330048"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="498564096"/>
+        <c:axId val="539353856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5396,12 +5454,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="498574080"/>
+        <c:crossAx val="539355392"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="498574080"/>
+        <c:axId val="539355392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5410,7 +5468,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="498564096"/>
+        <c:crossAx val="539353856"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5589,7 +5647,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5769,6 +5827,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5778,7 +5839,7 @@
               <c:f>'模型四 (3)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5957,6 +6018,9 @@
                   <c:v>81771837.474236697</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>81771837.474236697</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>81771837.474236697</c:v>
                 </c:pt>
               </c:numCache>
@@ -6000,7 +6064,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6180,6 +6244,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6189,7 +6256,7 @@
               <c:f>'模型四 (3)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6369,6 +6436,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>146690543.71748418</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>150074588.67072487</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6411,7 +6481,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6591,6 +6661,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6600,7 +6673,7 @@
               <c:f>'模型四 (3)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6780,6 +6853,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>64918706.243247479</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>68302751.196488172</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6801,11 +6877,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="498692096"/>
-        <c:axId val="498693632"/>
+        <c:axId val="539383680"/>
+        <c:axId val="539385216"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="498692096"/>
+        <c:axId val="539383680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6848,14 +6924,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="498693632"/>
+        <c:crossAx val="539385216"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="498693632"/>
+        <c:axId val="539385216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6906,7 +6982,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="498692096"/>
+        <c:crossAx val="539383680"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7097,7 +7173,7 @@
               <c:f>'模型四 (3)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7277,6 +7353,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-3004608.0591776534</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-13940556.981917825</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7296,8 +7375,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="498726016"/>
-        <c:axId val="498724224"/>
+        <c:axId val="539692032"/>
+        <c:axId val="539690496"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7322,7 +7401,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7502,6 +7581,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7511,7 +7593,7 @@
               <c:f>'模型四 (3)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7691,6 +7773,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7712,11 +7797,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="498721152"/>
-        <c:axId val="498722688"/>
+        <c:axId val="539425024"/>
+        <c:axId val="539688960"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="498721152"/>
+        <c:axId val="539425024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7759,14 +7844,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="498722688"/>
+        <c:crossAx val="539688960"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="498722688"/>
+        <c:axId val="539688960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7817,12 +7902,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="498721152"/>
+        <c:crossAx val="539425024"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="498724224"/>
+        <c:axId val="539690496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7859,12 +7944,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="498726016"/>
+        <c:crossAx val="539692032"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="498726016"/>
+        <c:axId val="539692032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7873,7 +7958,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="498724224"/>
+        <c:crossAx val="539690496"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8035,7 +8120,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8215,6 +8300,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-329147.77001413936</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-915628.10722505616</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8234,8 +8322,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="576074880"/>
-        <c:axId val="575946112"/>
+        <c:axId val="460511104"/>
+        <c:axId val="460508544"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -8260,7 +8348,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8440,6 +8528,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8449,7 +8540,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8629,6 +8720,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8650,11 +8744,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="575942656"/>
-        <c:axId val="575944576"/>
+        <c:axId val="460505472"/>
+        <c:axId val="460507008"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="575942656"/>
+        <c:axId val="460505472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8697,14 +8791,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="575944576"/>
+        <c:crossAx val="460507008"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="575944576"/>
+        <c:axId val="460507008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8755,12 +8849,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="575942656"/>
+        <c:crossAx val="460505472"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="575946112"/>
+        <c:axId val="460508544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8797,12 +8891,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="576074880"/>
+        <c:crossAx val="460511104"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="576074880"/>
+        <c:axId val="460511104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8811,7 +8905,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="575946112"/>
+        <c:crossAx val="460508544"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8990,7 +9084,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9170,6 +9264,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9179,7 +9276,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9358,6 +9455,9 @@
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>10887835.773480978</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
               </c:numCache>
@@ -9401,7 +9501,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9581,6 +9681,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9590,7 +9693,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9770,6 +9873,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>19051655.379257303</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>19503027.168851279</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9812,7 +9918,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9992,6 +10098,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10001,7 +10110,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10181,6 +10290,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>8163819.6057763249</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>8615191.3953703009</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10202,11 +10314,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="576258048"/>
-        <c:axId val="576259584"/>
+        <c:axId val="540192768"/>
+        <c:axId val="540194688"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="576258048"/>
+        <c:axId val="540192768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10249,14 +10361,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="576259584"/>
+        <c:crossAx val="540194688"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="576259584"/>
+        <c:axId val="540194688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10307,7 +10419,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="576258048"/>
+        <c:crossAx val="540192768"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10519,7 +10631,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10699,6 +10811,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-329147.77001413936</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-915628.10722505616</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10718,8 +10833,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="576491520"/>
-        <c:axId val="576374656"/>
+        <c:axId val="545083776"/>
+        <c:axId val="545081600"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10744,7 +10859,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10924,6 +11039,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10933,7 +11051,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -11113,6 +11231,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11134,11 +11255,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="576370944"/>
-        <c:axId val="576373120"/>
+        <c:axId val="545078272"/>
+        <c:axId val="545080064"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="576370944"/>
+        <c:axId val="545078272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11181,14 +11302,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="576373120"/>
+        <c:crossAx val="545080064"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="576373120"/>
+        <c:axId val="545080064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11239,12 +11360,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="576370944"/>
+        <c:crossAx val="545078272"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="576374656"/>
+        <c:axId val="545081600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11281,12 +11402,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="576491520"/>
+        <c:crossAx val="545083776"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="576491520"/>
+        <c:axId val="545083776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11295,7 +11416,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="576374656"/>
+        <c:crossAx val="545081600"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11474,7 +11595,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11654,6 +11775,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11663,7 +11787,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11842,6 +11966,9 @@
                   <c:v>96148460.828205004</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>96148460.828205004</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>96148460.828205004</c:v>
                 </c:pt>
               </c:numCache>
@@ -11885,7 +12012,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12065,6 +12192,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12074,7 +12204,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12254,6 +12384,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>171231537.50344989</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>175325159.08363307</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12296,7 +12429,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12476,6 +12609,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12485,7 +12621,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12665,6 +12801,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>75083076.675244883</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>79176698.255428061</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12686,11 +12825,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="576538496"/>
-        <c:axId val="576540032"/>
+        <c:axId val="549168256"/>
+        <c:axId val="549169792"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="576538496"/>
+        <c:axId val="549168256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12733,14 +12872,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="576540032"/>
+        <c:crossAx val="549169792"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="576540032"/>
+        <c:axId val="549169792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12791,7 +12930,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="576538496"/>
+        <c:crossAx val="549168256"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13003,7 +13142,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13183,6 +13322,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-3004608.0591776534</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-13940556.981917825</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13202,8 +13344,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="577215872"/>
-        <c:axId val="577213184"/>
+        <c:axId val="549837440"/>
+        <c:axId val="549835520"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -13228,7 +13370,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13408,6 +13550,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13417,7 +13562,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -13597,6 +13742,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13618,11 +13766,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="577029248"/>
-        <c:axId val="577030784"/>
+        <c:axId val="549794944"/>
+        <c:axId val="549796480"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="577029248"/>
+        <c:axId val="549794944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13665,14 +13813,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="577030784"/>
+        <c:crossAx val="549796480"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="577030784"/>
+        <c:axId val="549796480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13723,12 +13871,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="577029248"/>
+        <c:crossAx val="549794944"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="577213184"/>
+        <c:axId val="549835520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13765,12 +13913,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="577215872"/>
+        <c:crossAx val="549837440"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="577215872"/>
+        <c:axId val="549837440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13779,7 +13927,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="577213184"/>
+        <c:crossAx val="549835520"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13958,7 +14106,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14138,6 +14286,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14147,7 +14298,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14326,6 +14477,9 @@
                   <c:v>12402296.479929758</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>12402296.479929758</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>12402296.479929758</c:v>
                 </c:pt>
               </c:numCache>
@@ -14369,7 +14523,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14549,6 +14703,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14558,7 +14715,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14738,6 +14895,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>23978440.791011624</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>24560679.119701155</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14780,7 +14940,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14960,6 +15120,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14969,7 +15132,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15149,6 +15312,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>11576144.311081866</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>12158382.639771396</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15170,11 +15336,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="480139904"/>
-        <c:axId val="480153984"/>
+        <c:axId val="550043648"/>
+        <c:axId val="550045184"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="480139904"/>
+        <c:axId val="550043648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15217,14 +15383,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="480153984"/>
+        <c:crossAx val="550045184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="480153984"/>
+        <c:axId val="550045184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15275,7 +15441,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="480139904"/>
+        <c:crossAx val="550043648"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15466,7 +15632,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15646,6 +15812,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-290095.26738459605</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-1492008.3906064597</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15665,8 +15834,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="495099904"/>
-        <c:axId val="495098112"/>
+        <c:axId val="550762752"/>
+        <c:axId val="550760832"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -15691,7 +15860,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15871,6 +16040,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15880,7 +16052,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -16060,6 +16232,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16081,11 +16256,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="495086592"/>
-        <c:axId val="495096576"/>
+        <c:axId val="550396672"/>
+        <c:axId val="550398208"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="495086592"/>
+        <c:axId val="550396672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16128,14 +16303,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="495096576"/>
+        <c:crossAx val="550398208"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="495096576"/>
+        <c:axId val="550398208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16186,12 +16361,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="495086592"/>
+        <c:crossAx val="550396672"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="495098112"/>
+        <c:axId val="550760832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16228,12 +16403,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="495099904"/>
+        <c:crossAx val="550762752"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="495099904"/>
+        <c:axId val="550762752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16242,7 +16417,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="495098112"/>
+        <c:crossAx val="550760832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -16421,7 +16596,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16601,6 +16776,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16610,7 +16788,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16789,6 +16967,9 @@
                   <c:v>9534069.5785709675</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>9534069.5785709675</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>9534069.5785709675</c:v>
                 </c:pt>
               </c:numCache>
@@ -16832,7 +17013,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -17012,6 +17193,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17021,7 +17205,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17201,6 +17385,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>16815379.263691787</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>17195326.875446554</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17243,7 +17430,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -17423,6 +17610,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17432,7 +17622,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17612,6 +17802,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>7281309.6851208191</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>7661257.2968755867</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17633,11 +17826,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="495733760"/>
-        <c:axId val="495739648"/>
+        <c:axId val="576360832"/>
+        <c:axId val="576362752"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="495733760"/>
+        <c:axId val="576360832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17680,14 +17873,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="495739648"/>
+        <c:crossAx val="576362752"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="495739648"/>
+        <c:axId val="576362752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17738,7 +17931,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="495733760"/>
+        <c:crossAx val="576360832"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17839,7 +18032,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17877,7 +18070,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17920,7 +18113,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17958,7 +18151,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18001,7 +18194,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18039,7 +18232,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18082,7 +18275,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0300-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18120,7 +18313,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0300-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18163,7 +18356,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0400-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18201,7 +18394,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0400-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18244,7 +18437,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0500-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18282,7 +18475,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0500-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18325,7 +18518,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18363,7 +18556,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18674,7 +18867,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1"/>
@@ -21317,6 +21510,44 @@
         <v>1556201.7813372496</v>
       </c>
     </row>
+    <row r="63" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="32">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="31">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="31">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="29">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="29">
+        <v>-915628.10722505616</v>
+      </c>
+      <c r="F63" s="30">
+        <v>-717576.87366851489</v>
+      </c>
+      <c r="G63" s="30">
+        <v>11261973.499519134</v>
+      </c>
+      <c r="H63" s="30">
+        <v>14370278.443152532</v>
+      </c>
+      <c r="I63" s="30">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J63" s="30">
+        <v>16842108.331714839</v>
+      </c>
+      <c r="K63" s="30">
+        <v>7480773.5139874145</v>
+      </c>
+      <c r="L63" s="29">
+        <v>2471829.8885623058</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -21333,7 +21564,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH62"/>
+  <dimension ref="A1:AH63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -24677,6 +24908,56 @@
         <v>1</v>
       </c>
     </row>
+    <row r="63" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="31">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="16">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="17">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="17">
+        <v>-915628.10722505616</v>
+      </c>
+      <c r="F63" s="18">
+        <v>-717576.87366851489</v>
+      </c>
+      <c r="G63" s="18">
+        <v>13842794.925130703</v>
+      </c>
+      <c r="H63" s="18">
+        <v>17663406.641303208</v>
+      </c>
+      <c r="I63" s="18">
+        <v>10887835.773480978</v>
+      </c>
+      <c r="J63" s="18">
+        <v>19503027.168851279</v>
+      </c>
+      <c r="K63" s="18">
+        <v>8615191.3953703009</v>
+      </c>
+      <c r="L63" s="17">
+        <v>1839620.5275480719</v>
+      </c>
+      <c r="M63" s="22">
+        <v>4.3435412055936783E-2</v>
+      </c>
+      <c r="N63" s="22">
+        <v>5.037156159067379E-2</v>
+      </c>
+      <c r="O63" s="22">
+        <v>86.230028778736084</v>
+      </c>
+      <c r="P63" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -24693,7 +24974,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AH62"/>
+  <dimension ref="A1:AH63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -24728,10 +25009,10 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>3</v>
@@ -28034,6 +28315,56 @@
         <v>86.230028778736084</v>
       </c>
       <c r="P62" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="31">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="16">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="17">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="17">
+        <v>-13940556.981917825</v>
+      </c>
+      <c r="F63" s="18">
+        <v>-10925201.200517096</v>
+      </c>
+      <c r="G63" s="18">
+        <v>121127030.65179148</v>
+      </c>
+      <c r="H63" s="18">
+        <v>154558093.88406366</v>
+      </c>
+      <c r="I63" s="18">
+        <v>96148460.828205004</v>
+      </c>
+      <c r="J63" s="18">
+        <v>175325159.08363307</v>
+      </c>
+      <c r="K63" s="18">
+        <v>79176698.255428061</v>
+      </c>
+      <c r="L63" s="17">
+        <v>20767065.199569389</v>
+      </c>
+      <c r="M63" s="22">
+        <v>4.3435412055936783E-2</v>
+      </c>
+      <c r="N63" s="22">
+        <v>5.037156159067379E-2</v>
+      </c>
+      <c r="O63" s="22">
+        <v>86.230028778736084</v>
+      </c>
+      <c r="P63" s="1">
         <v>1</v>
       </c>
     </row>
@@ -28053,7 +28384,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AJ62"/>
+  <dimension ref="A1:AJ63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -28088,13 +28419,13 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>4</v>
@@ -31766,6 +32097,62 @@
         <v>86.230028778736084</v>
       </c>
       <c r="R62" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="31">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="16">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="17">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="17">
+        <v>3094800</v>
+      </c>
+      <c r="F63" s="17">
+        <v>4026308.4497372219</v>
+      </c>
+      <c r="G63" s="17">
+        <v>-1492008.3906064597</v>
+      </c>
+      <c r="H63" s="18">
+        <v>-1169285.5516015966</v>
+      </c>
+      <c r="I63" s="18">
+        <v>17612585.040835962</v>
+      </c>
+      <c r="J63" s="18">
+        <v>22473658.915226769</v>
+      </c>
+      <c r="K63" s="18">
+        <v>12402296.479929758</v>
+      </c>
+      <c r="L63" s="18">
+        <v>24560679.119701155</v>
+      </c>
+      <c r="M63" s="18">
+        <v>12158382.639771396</v>
+      </c>
+      <c r="N63" s="17">
+        <v>2087020.2044743849</v>
+      </c>
+      <c r="O63" s="22">
+        <v>4.3435412055936783E-2</v>
+      </c>
+      <c r="P63" s="22">
+        <v>5.037156159067379E-2</v>
+      </c>
+      <c r="Q63" s="22">
+        <v>86.230028778736084</v>
+      </c>
+      <c r="R63" s="1">
         <v>1</v>
       </c>
     </row>
@@ -31785,7 +32172,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AJ62"/>
+  <dimension ref="A1:AJ63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -31820,7 +32207,7 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>2</v>
@@ -31847,7 +32234,7 @@
         <v>9</v>
       </c>
       <c r="J1" s="39" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="K1" s="43" t="s">
         <v>11</v>
@@ -31856,19 +32243,19 @@
         <v>12</v>
       </c>
       <c r="M1" s="48" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N1" s="48" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P1" s="48" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -35325,6 +35712,59 @@
         <v>94.913940221952458</v>
       </c>
       <c r="Q62" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="31">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="16">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="17">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="17">
+        <v>-915628.10722505616</v>
+      </c>
+      <c r="F63" s="18">
+        <v>-717576.87366851489</v>
+      </c>
+      <c r="G63" s="18">
+        <v>11538790.535095841</v>
+      </c>
+      <c r="H63" s="18">
+        <v>14723496.986884249</v>
+      </c>
+      <c r="I63" s="18">
+        <v>9534069.5785709675</v>
+      </c>
+      <c r="J63" s="18">
+        <v>17195326.875446554</v>
+      </c>
+      <c r="K63" s="18">
+        <v>7661257.2968755867</v>
+      </c>
+      <c r="L63" s="17">
+        <v>2471829.8885623058</v>
+      </c>
+      <c r="M63" s="21">
+        <v>93.931398043426469</v>
+      </c>
+      <c r="N63" s="21">
+        <v>87.037193073217864</v>
+      </c>
+      <c r="O63" s="21">
+        <v>83.098819498850574</v>
+      </c>
+      <c r="P63" s="21">
+        <v>94.913940221952458</v>
+      </c>
+      <c r="Q63" s="1">
         <v>1</v>
       </c>
     </row>
@@ -35344,7 +35784,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AJ62"/>
+  <dimension ref="A1:AJ63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -38356,6 +38796,50 @@
         <v>6317428.3098842707</v>
       </c>
     </row>
+    <row r="63" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="31">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="16">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="17">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="17">
+        <v>3094800</v>
+      </c>
+      <c r="F63" s="17">
+        <v>4026308.4497372219</v>
+      </c>
+      <c r="G63" s="17">
+        <v>-10715332.987082755</v>
+      </c>
+      <c r="H63" s="18">
+        <v>-8397596.2342296485</v>
+      </c>
+      <c r="I63" s="18">
+        <v>107048806.88929719</v>
+      </c>
+      <c r="J63" s="18">
+        <v>136594280.04089597</v>
+      </c>
+      <c r="K63" s="18">
+        <v>77414706.150887698</v>
+      </c>
+      <c r="L63" s="18">
+        <v>153627041.337863</v>
+      </c>
+      <c r="M63" s="18">
+        <v>76212335.1869753</v>
+      </c>
+      <c r="N63" s="17">
+        <v>17032761.296967026</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="J2">
@@ -38372,7 +38856,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -38410,7 +38894,7 @@
         <v>18</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>3</v>
@@ -41013,6 +41497,44 @@
       </c>
       <c r="L62" s="17">
         <v>10783010.804513421</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="31">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="16">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="17">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="17">
+        <v>-13940556.981917825</v>
+      </c>
+      <c r="F63" s="18">
+        <v>-10925201.200517096</v>
+      </c>
+      <c r="G63" s="18">
+        <v>98237475.419918686</v>
+      </c>
+      <c r="H63" s="18">
+        <v>125351020.88429362</v>
+      </c>
+      <c r="I63" s="18">
+        <v>81771837.474236697</v>
+      </c>
+      <c r="J63" s="18">
+        <v>150074588.67072487</v>
+      </c>
+      <c r="K63" s="18">
+        <v>68302751.196488172</v>
+      </c>
+      <c r="L63" s="17">
+        <v>24723567.786431246</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(RSI&KDJ)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(RSI&KDJ)cn.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="36">
   <si>
     <t>in practice</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -125,10 +125,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>每年投入本金</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -149,6 +145,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>日期</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>SMA之MAX</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -165,6 +165,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>日期</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>深创100ETF</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -177,11 +181,19 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>SMA之MAX</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>成交量</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>成交均量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>利润</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -663,7 +675,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -849,6 +861,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -858,7 +873,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1043,6 +1058,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -1086,7 +1104,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1272,6 +1290,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1281,7 +1302,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1467,6 +1488,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>14938834.477348203</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>15015678.778184865</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1509,7 +1533,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1695,6 +1719,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1704,7 +1731,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1890,6 +1917,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>5577499.6596207786</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>5654343.9604574405</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1911,11 +1941,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="699167488"/>
-        <c:axId val="699169024"/>
+        <c:axId val="496866816"/>
+        <c:axId val="496868352"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="699167488"/>
+        <c:axId val="496866816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1958,14 +1988,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="699169024"/>
+        <c:crossAx val="496868352"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="699169024"/>
+        <c:axId val="496868352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2016,7 +2046,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="699167488"/>
+        <c:crossAx val="496866816"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2207,7 +2237,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2393,6 +2423,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-314574.39222416701</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-309173.41467680095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2412,8 +2445,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="692089216"/>
-        <c:axId val="692087424"/>
+        <c:axId val="495124864"/>
+        <c:axId val="495123072"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2438,7 +2471,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2624,6 +2657,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2633,7 +2669,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2819,6 +2855,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2840,11 +2879,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="564854144"/>
-        <c:axId val="692085888"/>
+        <c:axId val="495115648"/>
+        <c:axId val="495121536"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="564854144"/>
+        <c:axId val="495115648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2887,14 +2926,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692085888"/>
+        <c:crossAx val="495121536"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="692085888"/>
+        <c:axId val="495121536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2945,12 +2984,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="564854144"/>
+        <c:crossAx val="495115648"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="692087424"/>
+        <c:axId val="495123072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2987,12 +3026,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692089216"/>
+        <c:crossAx val="495124864"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="692089216"/>
+        <c:axId val="495124864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3001,7 +3040,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="692087424"/>
+        <c:crossAx val="495123072"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3180,7 +3219,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3366,6 +3405,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3375,7 +3417,7 @@
               <c:f>'模型四 (3)PE副本成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3560,6 +3602,9 @@
                   <c:v>77414706.150887698</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>77414706.150887698</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>77414706.150887698</c:v>
                 </c:pt>
               </c:numCache>
@@ -3603,7 +3648,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3789,6 +3834,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3798,7 +3846,7 @@
               <c:f>'模型四 (3)PE副本成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3984,6 +4032,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>135535789.80879113</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>136265288.66553408</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4026,7 +4077,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4212,6 +4263,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4221,7 +4275,7 @@
               <c:f>'模型四 (3)PE副本成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4407,6 +4461,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>58121083.657903433</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>58850582.514646381</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4428,11 +4485,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="692112768"/>
-        <c:axId val="693105792"/>
+        <c:axId val="495295872"/>
+        <c:axId val="495522944"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="692112768"/>
+        <c:axId val="495295872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4475,14 +4532,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="693105792"/>
+        <c:crossAx val="495522944"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="693105792"/>
+        <c:axId val="495522944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4533,7 +4590,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692112768"/>
+        <c:crossAx val="495295872"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4724,7 +4781,7 @@
               <c:f>'模型四 (3)PE副本成交量'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4910,6 +4967,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-3137492.7659313167</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-1153306.5826965235</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4929,8 +4989,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="693539584"/>
-        <c:axId val="693136384"/>
+        <c:axId val="495571712"/>
+        <c:axId val="495553536"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4955,7 +5015,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5141,6 +5201,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5150,7 +5213,7 @@
               <c:f>'模型四 (3)PE副本成交量'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5336,6 +5399,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5357,11 +5423,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="693133312"/>
-        <c:axId val="693134848"/>
+        <c:axId val="495550464"/>
+        <c:axId val="495552000"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="693133312"/>
+        <c:axId val="495550464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5404,14 +5470,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="693134848"/>
+        <c:crossAx val="495552000"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="693134848"/>
+        <c:axId val="495552000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5462,12 +5528,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="693133312"/>
+        <c:crossAx val="495550464"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="693136384"/>
+        <c:axId val="495553536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5504,12 +5570,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="693539584"/>
+        <c:crossAx val="495571712"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="693539584"/>
+        <c:axId val="495571712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5518,7 +5584,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="693136384"/>
+        <c:crossAx val="495553536"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5697,7 +5763,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5883,6 +5949,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5892,7 +5961,7 @@
               <c:f>'模型四 (3)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6077,6 +6146,9 @@
                   <c:v>81771837.474236697</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>81771837.474236697</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>81771837.474236697</c:v>
                 </c:pt>
               </c:numCache>
@@ -6120,7 +6192,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6306,6 +6378,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6315,7 +6390,7 @@
               <c:f>'模型四 (3)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6501,6 +6576,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>133472452.42047533</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>134142360.25154558</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6543,7 +6621,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6729,6 +6807,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6738,7 +6819,7 @@
               <c:f>'模型四 (3)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6924,6 +7005,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>51700614.946238637</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>52370522.777308881</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6945,11 +7029,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="693874688"/>
-        <c:axId val="693876224"/>
+        <c:axId val="495669248"/>
+        <c:axId val="495670784"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="693874688"/>
+        <c:axId val="495669248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6992,14 +7076,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="693876224"/>
+        <c:crossAx val="495670784"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="693876224"/>
+        <c:axId val="495670784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7050,7 +7134,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="693874688"/>
+        <c:crossAx val="495669248"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7241,7 +7325,7 @@
               <c:f>'模型四 (3)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7427,6 +7511,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-2807284.9763754238</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-2735298.1140760505</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7446,8 +7533,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="694834304"/>
-        <c:axId val="694832512"/>
+        <c:axId val="495707264"/>
+        <c:axId val="495705472"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7472,7 +7559,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7658,6 +7745,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7667,7 +7757,7 @@
               <c:f>'模型四 (3)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7853,6 +7943,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7874,11 +7967,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="694829440"/>
-        <c:axId val="694830976"/>
+        <c:axId val="495702400"/>
+        <c:axId val="495703936"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="694829440"/>
+        <c:axId val="495702400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7921,14 +8014,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="694830976"/>
+        <c:crossAx val="495703936"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="694830976"/>
+        <c:axId val="495703936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7979,12 +8072,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="694829440"/>
+        <c:crossAx val="495702400"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="694832512"/>
+        <c:axId val="495705472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8021,12 +8114,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="694834304"/>
+        <c:crossAx val="495707264"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="694834304"/>
+        <c:axId val="495707264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8035,7 +8128,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="694832512"/>
+        <c:crossAx val="495705472"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8197,7 +8290,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8383,6 +8476,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-314574.39222416701</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-309173.41467680095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8402,8 +8498,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="703800448"/>
-        <c:axId val="703798656"/>
+        <c:axId val="506356096"/>
+        <c:axId val="506308864"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -8428,7 +8524,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8614,6 +8710,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8623,7 +8722,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8809,6 +8908,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8830,11 +8932,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="703795200"/>
-        <c:axId val="703797120"/>
+        <c:axId val="506298368"/>
+        <c:axId val="506306560"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="703795200"/>
+        <c:axId val="506298368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8877,14 +8979,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="703797120"/>
+        <c:crossAx val="506306560"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="703797120"/>
+        <c:axId val="506306560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8935,12 +9037,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="703795200"/>
+        <c:crossAx val="506298368"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="703798656"/>
+        <c:axId val="506308864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8977,12 +9079,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="703800448"/>
+        <c:crossAx val="506356096"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="703800448"/>
+        <c:axId val="506356096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8991,7 +9093,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="703798656"/>
+        <c:crossAx val="506308864"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9170,7 +9272,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9356,6 +9458,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9365,7 +9470,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9550,6 +9655,9 @@
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>10887835.773480978</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
               </c:numCache>
@@ -9593,7 +9701,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9779,6 +9887,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9788,7 +9899,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9974,6 +10085,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>17163594.417257134</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>17258504.389312655</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10016,7 +10130,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10202,6 +10316,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10211,7 +10328,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10397,6 +10514,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>6275758.643776156</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>6370668.6158316769</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10418,11 +10538,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="703820160"/>
-        <c:axId val="703821696"/>
+        <c:axId val="506377728"/>
+        <c:axId val="506405248"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="703820160"/>
+        <c:axId val="506377728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10465,14 +10585,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="703821696"/>
+        <c:crossAx val="506405248"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="703821696"/>
+        <c:axId val="506405248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10523,7 +10643,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="703820160"/>
+        <c:crossAx val="506377728"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10735,7 +10855,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10921,6 +11041,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-314574.39222416701</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-61834.682935360193</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10940,8 +11063,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="704064128"/>
-        <c:axId val="704062208"/>
+        <c:axId val="506530816"/>
+        <c:axId val="506529280"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10966,7 +11089,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11152,6 +11275,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11161,7 +11287,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -11347,6 +11473,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11368,11 +11497,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="703976576"/>
-        <c:axId val="703978496"/>
+        <c:axId val="506517376"/>
+        <c:axId val="506527744"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="703976576"/>
+        <c:axId val="506517376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11415,14 +11544,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="703978496"/>
+        <c:crossAx val="506527744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="703978496"/>
+        <c:axId val="506527744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11473,12 +11602,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="703976576"/>
+        <c:crossAx val="506517376"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="704062208"/>
+        <c:axId val="506529280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11515,12 +11644,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="704064128"/>
+        <c:crossAx val="506530816"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="704064128"/>
+        <c:axId val="506530816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11529,7 +11658,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="704062208"/>
+        <c:crossAx val="506529280"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11708,7 +11837,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11894,6 +12023,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11903,7 +12035,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12088,6 +12220,9 @@
                   <c:v>96148460.828205004</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>96148460.828205004</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>96148460.828205004</c:v>
                 </c:pt>
               </c:numCache>
@@ -12131,7 +12266,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12317,6 +12452,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12326,7 +12464,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12512,6 +12650,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>154854687.32249239</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>155684821.34165195</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12554,7 +12695,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12740,6 +12881,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12749,7 +12893,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12935,6 +13079,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>58706226.494287387</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>59536360.513446942</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12956,11 +13103,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="704331776"/>
-        <c:axId val="704333312"/>
+        <c:axId val="506695680"/>
+        <c:axId val="506697984"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="704331776"/>
+        <c:axId val="506695680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13003,14 +13150,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="704333312"/>
+        <c:crossAx val="506697984"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="704333312"/>
+        <c:axId val="506697984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13061,7 +13208,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="704331776"/>
+        <c:crossAx val="506695680"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13273,7 +13420,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13459,6 +13606,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-2807284.9763754238</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-547059.62281521014</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13478,8 +13628,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="704791680"/>
-        <c:axId val="704736640"/>
+        <c:axId val="507057280"/>
+        <c:axId val="506972800"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -13504,7 +13654,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13690,6 +13840,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13699,7 +13852,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -13885,6 +14038,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13906,11 +14062,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="704707968"/>
-        <c:axId val="704734720"/>
+        <c:axId val="506850304"/>
+        <c:axId val="506970880"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="704707968"/>
+        <c:axId val="506850304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13953,14 +14109,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="704734720"/>
+        <c:crossAx val="506970880"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="704734720"/>
+        <c:axId val="506970880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14011,12 +14167,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="704707968"/>
+        <c:crossAx val="506850304"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="704736640"/>
+        <c:axId val="506972800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14053,12 +14209,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="704791680"/>
+        <c:crossAx val="507057280"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="704791680"/>
+        <c:axId val="507057280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14067,7 +14223,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="704736640"/>
+        <c:crossAx val="506972800"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -14246,7 +14402,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14432,6 +14588,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14441,7 +14600,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14626,6 +14785,9 @@
                   <c:v>12402296.479929758</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>12402296.479929758</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>12402296.479929758</c:v>
                 </c:pt>
               </c:numCache>
@@ -14669,7 +14831,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14855,6 +15017,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14864,7 +15029,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15050,6 +15215,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>21584151.727103103</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>21704676.819443233</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15092,7 +15260,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15278,6 +15446,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15287,7 +15458,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15473,6 +15644,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>9181855.2471733447</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>9302380.3395134751</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15494,11 +15668,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="728770048"/>
-        <c:axId val="729563136"/>
+        <c:axId val="507107584"/>
+        <c:axId val="507319424"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="728770048"/>
+        <c:axId val="507107584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15541,14 +15715,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="729563136"/>
+        <c:crossAx val="507319424"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="729563136"/>
+        <c:axId val="507319424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15599,7 +15773,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="728770048"/>
+        <c:crossAx val="507107584"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15790,7 +15964,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15976,6 +16150,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-436866.08133220871</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-32117.398505472807</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15995,8 +16172,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="555794432"/>
-        <c:axId val="555792640"/>
+        <c:axId val="424706048"/>
+        <c:axId val="532273408"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -16021,7 +16198,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16207,6 +16384,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16216,7 +16396,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -16402,6 +16582,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16423,11 +16606,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="555785216"/>
-        <c:axId val="555791104"/>
+        <c:axId val="531573376"/>
+        <c:axId val="532271488"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="555785216"/>
+        <c:axId val="531573376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16470,14 +16653,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="555791104"/>
+        <c:crossAx val="532271488"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="555791104"/>
+        <c:axId val="532271488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16528,12 +16711,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="555785216"/>
+        <c:crossAx val="531573376"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="555792640"/>
+        <c:axId val="532273408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16570,12 +16753,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="555794432"/>
+        <c:crossAx val="424706048"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="555794432"/>
+        <c:axId val="424706048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16584,7 +16767,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="555792640"/>
+        <c:crossAx val="532273408"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -16763,7 +16946,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16949,6 +17132,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16958,7 +17144,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17143,6 +17329,9 @@
                   <c:v>9534069.5785709675</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>9534069.5785709675</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>9534069.5785709675</c:v>
                 </c:pt>
               </c:numCache>
@@ -17186,7 +17375,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -17372,6 +17561,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17381,7 +17573,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17567,6 +17759,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>15245270.933883663</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>15324052.945521576</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17609,7 +17804,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -17795,6 +17990,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17804,7 +18002,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17990,6 +18188,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>5711201.3553126957</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>5789983.3669506088</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18011,11 +18212,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="555990016"/>
-        <c:axId val="556086016"/>
+        <c:axId val="490339328"/>
+        <c:axId val="490607360"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="555990016"/>
+        <c:axId val="490339328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -18058,14 +18259,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556086016"/>
+        <c:crossAx val="490607360"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="556086016"/>
+        <c:axId val="490607360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -18116,7 +18317,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="555990016"/>
+        <c:crossAx val="490339328"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -19052,7 +19253,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1"/>
@@ -19183,28 +19384,28 @@
       </c>
       <c r="M3" s="27"/>
       <c r="P3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="46" t="s">
+      <c r="R3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="R3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="W3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="W3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -21769,6 +21970,44 @@
       </c>
       <c r="L64" s="29">
         <v>2786404.2807864728</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="32">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="31">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="31">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="29">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="29">
+        <v>-309173.41467680095</v>
+      </c>
+      <c r="F65" s="30">
+        <v>-277534.492817975</v>
+      </c>
+      <c r="G65" s="30">
+        <v>10700270.628994567</v>
+      </c>
+      <c r="H65" s="30">
+        <v>11920101.082721591</v>
+      </c>
+      <c r="I65" s="30">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J65" s="30">
+        <v>15015678.778184865</v>
+      </c>
+      <c r="K65" s="30">
+        <v>5654343.9604574405</v>
+      </c>
+      <c r="L65" s="29">
+        <v>3095577.6954632737</v>
       </c>
     </row>
   </sheetData>
@@ -21787,7 +22026,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH64"/>
+  <dimension ref="A1:AH65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -21822,7 +22061,7 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>2</v>
@@ -21929,28 +22168,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="R3" s="46" t="s">
+      <c r="S3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="S3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="X3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="X3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -25229,6 +25468,56 @@
       </c>
       <c r="P64" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="31">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="16">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="17">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="17">
+        <v>-61834.682935360193</v>
+      </c>
+      <c r="F65" s="18">
+        <v>-55506.898563595001</v>
+      </c>
+      <c r="G65" s="18">
+        <v>13503119.648860516</v>
+      </c>
+      <c r="H65" s="18">
+        <v>15042474.786605056</v>
+      </c>
+      <c r="I65" s="18">
+        <v>10887835.773480978</v>
+      </c>
+      <c r="J65" s="18">
+        <v>17258504.389312655</v>
+      </c>
+      <c r="K65" s="18">
+        <v>6370668.6158316769</v>
+      </c>
+      <c r="L65" s="17">
+        <v>2216029.6027075993</v>
+      </c>
+      <c r="M65" s="22">
+        <v>2.9890860469234198E-2</v>
+      </c>
+      <c r="N65" s="22">
+        <v>5.7377062222749194E-2</v>
+      </c>
+      <c r="O65" s="22">
+        <v>52.095487833085492</v>
+      </c>
+      <c r="P65" s="1">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -25247,7 +25536,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AH64"/>
+  <dimension ref="A1:AH65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -25282,16 +25571,16 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -25318,7 +25607,7 @@
         <v>12</v>
       </c>
       <c r="M1" s="44" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="N1" s="44" t="s">
         <v>20</v>
@@ -25389,28 +25678,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="R3" s="46" t="s">
+      <c r="S3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="S3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="X3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="X3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -28689,6 +28978,56 @@
       </c>
       <c r="P64" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="31">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="16">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="17">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="17">
+        <v>-547059.62281521014</v>
+      </c>
+      <c r="F65" s="18">
+        <v>-491076.87709154305</v>
+      </c>
+      <c r="G65" s="18">
+        <v>118100014.30468671</v>
+      </c>
+      <c r="H65" s="18">
+        <v>131563411.54289193</v>
+      </c>
+      <c r="I65" s="18">
+        <v>96148460.828205004</v>
+      </c>
+      <c r="J65" s="18">
+        <v>155684821.34165195</v>
+      </c>
+      <c r="K65" s="18">
+        <v>59536360.513446942</v>
+      </c>
+      <c r="L65" s="17">
+        <v>24121409.798760023</v>
+      </c>
+      <c r="M65" s="22">
+        <v>2.9890860469234198E-2</v>
+      </c>
+      <c r="N65" s="22">
+        <v>5.7377062222749194E-2</v>
+      </c>
+      <c r="O65" s="22">
+        <v>52.095487833085492</v>
+      </c>
+      <c r="P65" s="1">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -28707,7 +29046,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AJ64"/>
+  <dimension ref="A1:AJ65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -28742,22 +29081,22 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>5</v>
@@ -28778,13 +29117,13 @@
         <v>10</v>
       </c>
       <c r="M1" s="43" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="N1" s="44" t="s">
         <v>12</v>
       </c>
       <c r="O1" s="44" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="P1" s="44" t="s">
         <v>20</v>
@@ -28867,28 +29206,28 @@
       <c r="P3" s="22"/>
       <c r="Q3" s="22"/>
       <c r="S3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="U3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="Z3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -32533,6 +32872,62 @@
       </c>
       <c r="R64" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="31">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="16">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="17">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="17">
+        <v>1687200</v>
+      </c>
+      <c r="F65" s="17">
+        <v>4001533.5447742641</v>
+      </c>
+      <c r="G65" s="17">
+        <v>-32117.398505472807</v>
+      </c>
+      <c r="H65" s="18">
+        <v>-28830.699800522107</v>
+      </c>
+      <c r="I65" s="18">
+        <v>17189114.698789086</v>
+      </c>
+      <c r="J65" s="18">
+        <v>19148673.135131169</v>
+      </c>
+      <c r="K65" s="18">
+        <v>12402296.479929758</v>
+      </c>
+      <c r="L65" s="18">
+        <v>21704676.819443233</v>
+      </c>
+      <c r="M65" s="18">
+        <v>9302380.3395134751</v>
+      </c>
+      <c r="N65" s="17">
+        <v>2556003.6843120661</v>
+      </c>
+      <c r="O65" s="22">
+        <v>2.9890860469234198E-2</v>
+      </c>
+      <c r="P65" s="22">
+        <v>5.7377062222749194E-2</v>
+      </c>
+      <c r="Q65" s="22">
+        <v>52.095487833085492</v>
+      </c>
+      <c r="R65" s="1">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -32551,7 +32946,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AJ64"/>
+  <dimension ref="A1:AJ65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -32586,10 +32981,10 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>3</v>
@@ -32622,19 +33017,19 @@
         <v>12</v>
       </c>
       <c r="M1" s="48" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="N1" s="48" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="P1" s="48" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -32712,28 +33107,28 @@
         <v>1</v>
       </c>
       <c r="S3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="U3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="Z3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -36197,6 +36592,59 @@
         <v>53.045574900238108</v>
       </c>
       <c r="Q64" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="31">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="16">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="17">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="17">
+        <v>-309173.41467680095</v>
+      </c>
+      <c r="F65" s="18">
+        <v>-277534.492817975</v>
+      </c>
+      <c r="G65" s="18">
+        <v>10977087.664571274</v>
+      </c>
+      <c r="H65" s="18">
+        <v>12228475.250058303</v>
+      </c>
+      <c r="I65" s="18">
+        <v>9534069.5785709675</v>
+      </c>
+      <c r="J65" s="18">
+        <v>15324052.945521576</v>
+      </c>
+      <c r="K65" s="18">
+        <v>5789983.3669506088</v>
+      </c>
+      <c r="L65" s="17">
+        <v>3095577.6954632737</v>
+      </c>
+      <c r="M65" s="21">
+        <v>31.202982920806502</v>
+      </c>
+      <c r="N65" s="21">
+        <v>57.963077631244182</v>
+      </c>
+      <c r="O65" s="21">
+        <v>72.982292563465052</v>
+      </c>
+      <c r="P65" s="21">
+        <v>27.924647766802451</v>
+      </c>
+      <c r="Q65" s="1">
         <v>1</v>
       </c>
     </row>
@@ -36216,7 +36664,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AJ64"/>
+  <dimension ref="A1:AJ65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -36254,19 +36702,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>5</v>
@@ -36362,28 +36810,28 @@
       </c>
       <c r="O3" s="7"/>
       <c r="S3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="U3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="Z3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -39314,6 +39762,50 @@
       </c>
       <c r="N64" s="17">
         <v>20170254.062898342</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="31">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="16">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="17">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="17">
+        <v>1687200</v>
+      </c>
+      <c r="F65" s="17">
+        <v>4001533.5447742641</v>
+      </c>
+      <c r="G65" s="17">
+        <v>-1153306.5826965235</v>
+      </c>
+      <c r="H65" s="18">
+        <v>-1035284.2201096574</v>
+      </c>
+      <c r="I65" s="18">
+        <v>103179292.51123646</v>
+      </c>
+      <c r="J65" s="18">
+        <v>114941728.0199392</v>
+      </c>
+      <c r="K65" s="18">
+        <v>77414706.150887698</v>
+      </c>
+      <c r="L65" s="18">
+        <v>136265288.66553408</v>
+      </c>
+      <c r="M65" s="18">
+        <v>58850582.514646381</v>
+      </c>
+      <c r="N65" s="17">
+        <v>21323560.645594865</v>
       </c>
     </row>
   </sheetData>
@@ -39332,7 +39824,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -39367,7 +39859,7 @@
   <sheetData>
     <row r="1" spans="1:33" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>2</v>
@@ -39463,28 +39955,28 @@
       </c>
       <c r="M3" s="7"/>
       <c r="P3" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="46" t="s">
+      <c r="R3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="R3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="W3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="W3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -42049,6 +42541,44 @@
       </c>
       <c r="L64" s="17">
         <v>27530852.762806669</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="31">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="16">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="17">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="17">
+        <v>-2735298.1140760505</v>
+      </c>
+      <c r="F65" s="18">
+        <v>-2455384.385457715</v>
+      </c>
+      <c r="G65" s="18">
+        <v>93246151.564447746</v>
+      </c>
+      <c r="H65" s="18">
+        <v>103876209.37466286</v>
+      </c>
+      <c r="I65" s="18">
+        <v>81771837.474236697</v>
+      </c>
+      <c r="J65" s="18">
+        <v>134142360.25154558</v>
+      </c>
+      <c r="K65" s="18">
+        <v>52370522.777308881</v>
+      </c>
+      <c r="L65" s="17">
+        <v>30266150.876882721</v>
       </c>
     </row>
   </sheetData>
